--- a/product-definitions/spreadsheet/sf6-concentration.xlsx
+++ b/product-definitions/spreadsheet/sf6-concentration.xlsx
@@ -1955,7 +1955,7 @@
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
       <c r="B21" s="6" t="s">
         <v>19</v>
@@ -1970,7 +1970,7 @@
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
       <c r="B22" s="6" t="s">
         <v>20</v>
@@ -1985,7 +1985,7 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>22</v>
@@ -2000,7 +2000,7 @@
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
         <v>23</v>
@@ -2015,7 +2015,7 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
       <c r="B25" s="6" t="s">
         <v>25</v>
@@ -2030,7 +2030,7 @@
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="7" t="s">
         <v>26</v>
@@ -2045,7 +2045,7 @@
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6" t="s">
         <v>28</v>
@@ -2060,7 +2060,7 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="17" t="s">
         <v>30</v>
@@ -2075,7 +2075,7 @@
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="8"/>
@@ -2086,7 +2086,7 @@
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="12" t="s">
         <v>35</v>
       </c>
@@ -2099,7 +2099,7 @@
       <c r="H30" s="6"/>
       <c r="I30" s="6"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6" t="s">
         <v>10</v>
@@ -2114,7 +2114,7 @@
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6" t="s">
         <v>12</v>
@@ -2129,7 +2129,7 @@
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="7"/>
       <c r="B33" s="7" t="s">
         <v>2</v>
@@ -2144,7 +2144,7 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6" t="s">
         <v>19</v>
@@ -2159,7 +2159,7 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6" t="s">
         <v>20</v>
@@ -2174,7 +2174,7 @@
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="6"/>
       <c r="B36" s="6" t="s">
         <v>22</v>
@@ -2189,7 +2189,7 @@
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6" t="s">
         <v>23</v>
@@ -2204,7 +2204,7 @@
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="6"/>
       <c r="B38" s="6" t="s">
         <v>25</v>
@@ -2219,7 +2219,7 @@
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="7" t="s">
         <v>26</v>
@@ -2234,7 +2234,7 @@
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="6"/>
       <c r="B40" s="6" t="s">
         <v>28</v>
@@ -2249,7 +2249,7 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6"/>
       <c r="B41" s="17" t="s">
         <v>30</v>
@@ -2264,7 +2264,7 @@
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -2275,7 +2275,7 @@
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="12" t="s">
         <v>38</v>
       </c>
@@ -2288,7 +2288,7 @@
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="6"/>
       <c r="B44" s="6" t="s">
         <v>10</v>
@@ -2303,7 +2303,7 @@
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="6" t="s">
         <v>12</v>
@@ -2318,7 +2318,7 @@
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="7"/>
       <c r="B46" s="7" t="s">
         <v>2</v>
@@ -2333,7 +2333,7 @@
       <c r="H46" s="6"/>
       <c r="I46" s="6"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="6"/>
       <c r="B47" s="6" t="s">
         <v>19</v>
@@ -2348,7 +2348,7 @@
       <c r="H47" s="6"/>
       <c r="I47" s="6"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="6"/>
       <c r="B48" s="6" t="s">
         <v>20</v>
@@ -2363,7 +2363,7 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="6"/>
       <c r="B49" s="6" t="s">
         <v>22</v>
@@ -2378,7 +2378,7 @@
       <c r="H49" s="6"/>
       <c r="I49" s="6"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="6"/>
       <c r="B50" s="6" t="s">
         <v>23</v>
@@ -2393,7 +2393,7 @@
       <c r="H50" s="6"/>
       <c r="I50" s="6"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="6"/>
       <c r="B51" s="6" t="s">
         <v>25</v>
@@ -2408,7 +2408,7 @@
       <c r="H51" s="6"/>
       <c r="I51" s="6"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="6"/>
       <c r="B52" s="7" t="s">
         <v>26</v>
@@ -2423,7 +2423,7 @@
       <c r="H52" s="6"/>
       <c r="I52" s="6"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="6"/>
       <c r="B53" s="6" t="s">
         <v>28</v>
@@ -2438,7 +2438,7 @@
       <c r="H53" s="6"/>
       <c r="I53" s="6"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="6"/>
       <c r="B54" s="17" t="s">
         <v>30</v>
@@ -2453,7 +2453,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="6"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -2464,7 +2464,7 @@
       <c r="H55" s="6"/>
       <c r="I55" s="6"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="6" t="s">
         <v>41</v>
       </c>
@@ -2477,7 +2477,7 @@
       <c r="H56" s="6"/>
       <c r="I56" s="6"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="6"/>
       <c r="B57" s="6" t="s">
         <v>10</v>
@@ -2492,7 +2492,7 @@
       <c r="H57" s="6"/>
       <c r="I57" s="6"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="6"/>
       <c r="B58" s="6" t="s">
         <v>12</v>
@@ -2507,7 +2507,7 @@
       <c r="H58" s="6"/>
       <c r="I58" s="6"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6"/>
       <c r="B59" s="6" t="s">
         <v>2</v>
@@ -2522,7 +2522,7 @@
       <c r="H59" s="6"/>
       <c r="I59" s="6"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="6"/>
       <c r="B60" s="6" t="s">
         <v>19</v>
@@ -2535,7 +2535,7 @@
       <c r="H60" s="6"/>
       <c r="I60" s="6"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="6"/>
       <c r="B61" s="6" t="s">
         <v>20</v>
@@ -2550,7 +2550,7 @@
       <c r="H61" s="6"/>
       <c r="I61" s="6"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="6"/>
       <c r="B62" s="6" t="s">
         <v>44</v>
@@ -2565,7 +2565,7 @@
       <c r="H62" s="6"/>
       <c r="I62" s="6"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="6"/>
       <c r="B63" s="8" t="s">
         <v>46</v>
